--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0093.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0093.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Chìm Dưới Thủy Triều</t>
+          <t>Chìm Sâu Dưới Làn Sóng</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Humanity Has Declined</t>
+          <t>Loài Người Đã Suy Tàn</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Thế Giới Tatami Trong Ba Lô</t>
+          <t>Thiên Hà Tatami Trong Ba Lô</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>My Most Precious Treasure</t>
+          <t>Kho Báu Quý Giá Nhất Của Ta</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Một Namipon Để Bắt Đầu</t>
+          <t>Một Đồng Namipon Để Bắt Đầu</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Oddity's Ender</t>
+          <t>Kẻ Diệt Kỳ Lạ</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Capybara Ninja! Sức Mạnh Loài Gặm Nhấm!</t>
+          <t>Linh Cẩu Ninja! Sức mạnh loài gặm nhấm!</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Đến Tận Cùng Thế Gian</t>
+          <t>Cho Đến Ngày Tận Thế</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Tất Cả Những Câu Chuyện Được Tìm Thấy Lại</t>
+          <t>Tất cả những Truyện Cổ Tích Được Tìm Thấy</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Điểm Kết Thúc Của Hành Lang Mùa Hè</t>
+          <t>Hết Lối Đi Đến Mùa Hè</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>"Passione"</t>
+          <t>"Đam mê"</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sunny Sunny Delight</t>
+          <t>Niềm Vui Nắng Ấm</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Đọc tin nhắn viết nguệch ngoạc trên chiếc ô trong Hành Lang Meishin</t>
+          <t>Đọc dòng chữ nguệch ngoạc trên chiếc ô ở Hành lang Meishin</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Nhiệm Vụ Chính - Đoạn Nối "Ánh Sao Chảy Trong Mống Mắt" để mở khóa</t>
+          <t>Hoàn thành Chương II - Đoạn Nối "Ánh Sao Lấp Lánh Trong Mống Mắt" của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Ánh Sao Chảy Trong Mống Mắt" để mở khóa</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Ánh Sao Lấp Lánh Trong Mống Mắt" để mở khóa</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Eternal Finale</t>
+          <t>Khúc Kết Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Viễn Cảnh Của Những Lời Thì Thầm</t>
+          <t>Thế Giới Bên Kia Của Những Lời Thì Thầm</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Khúc Bi Ca Dành Cho Chính Mình</t>
+          <t>Khúc Bi Ca Dành Tặng Chính Mình</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Infernal Symphony</t>
+          <t>Bản Giao Hưởng Hỏa Ngục</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Silent Illusions</t>
+          <t>Ảo Ảnh Vô Thanh</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Đã đặt lại hoàn tất</t>
+          <t>Đặt lại hoàn tất</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Burning Waves Starts</t>
+          <t>Hiệu Ứng Sóng Lửa Bắt Đầu</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Burning Waves Ends</t>
+          <t>Hiệu Ứng Sóng Lửa Kết Thúc</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Magnetism Before Light</t>
+          <t>Magnet Trước Ánh Sáng</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Mu Xueting</t>
+          <t>Mộ Tuyết Đình</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Stasis, Cycle, Renewal</t>
+          <t>Trì Tĩnh, Chu Kỳ, Tái Sinh</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Jiang Yingjun</t>
+          <t>Khương Anh Quân</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Ấn Chương Mặt Trời và Griffin</t>
+          <t>Ấn Triện Mặt Trời và Griffin</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Old Headband</t>
+          <t>Băng Đô Cũ</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>"Little Acorniator"</t>
+          <t>"Cậu Bé Hạt Dẻ Nhí"</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Broken Rebirth</t>
+          <t>Sự Tái Sinh Vỡ</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Lightly Tossed Suspense</t>
+          <t>Hồi Hộp Nhẹ Nhàng</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Sự Vĩnh Cửu Đo Bằng Khoảnh Khắc</t>
+          <t>Vĩnh Cửu Đong Đếm Bằng Khoảnh Khắc</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>The Whisper</t>
+          <t>Lời Thì Thầm</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>The "Flawless" Hero</t>
+          <t>Anh Hùng "Hoàn Hảo"</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Ngai Vàng Gai Nhọn</t>
+          <t>Ngai Gai</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Một Ngày Nào Đó, Trong Đấu Trường...</t>
+          <t>Một Ngày Nào Đó, Tại Đấu Trường...</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Ta Dâng Ngươi Nỗi Đắng Của Kẻ Ngắm Trăng</t>
+          <t>Ta Dâng Tặng Ngươi Nỗi Đắng Cay Của Kẻ Ngắm Trăng</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Ngàn Lần Trăng Đã Rơi</t>
+          <t>Ngàn Lần Trăng Tà Đổ Xuống</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Cuối cùng, Chu kỳ lại Bắt đầu</t>
+          <t>Cuối Cùng, Vòng Luân Hồi Lại Bắt Đầu</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Jinzhou Rising</t>
+          <t>Jinzhou Trỗi Dậy</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Hành trình mới đang chờ đợi</t>
+          <t>Hành trình mới đang chờ đón</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Hành trình mới đang chờ đợi</t>
+          <t>Hành trình mới đang chờ đón</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Update Notification Options</t>
+          <t>Cập nhật Tùy chọn Thông báo</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Bạn đang sử dụng phiên bản mới nhất</t>
+          <t>Cậu đang dùng phiên bản mới nhất</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Phiên bản mới đã có sẵn</t>
+          <t>Phiên bản mới đã có</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Ignore</t>
+          <t>Bỏ qua</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chung</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Dreamscape Energy</t>
+          <t>Năng Lượng Cảnh Mộng</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Blazing Star</t>
+          <t>Ngôi Sao Rực Lửa</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Rampage</t>
+          <t>Cuồng Nộ</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Current Wave:</t>
+          <t>Làn Sóng Hiện Tại:</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Chest Wave</t>
+          <t>Cơn sóng rương kho báu</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Infinite Wave</t>
+          <t>Sóng Vô Tận</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Chế độ Helltide bị khóa</t>
+          <t>Chế Độ Hắc Triều đã bị khóa</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Dùng Augusta để vượt qua Tầng 1 đến Tầng 4 Tháp Hazard trong Tháp Nghịch Cảnh: Khu Vực Hazard</t>
+          <t>Dùng Augusta để vượt từ tầng 1 đến tầng 4 của Hazard Tower trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Dùng Iuno để vượt qua Tầng 1 đến Tầng 4 Tháp Hazard trong Tháp Nghịch Cảnh: Khu Vực Hazard</t>
+          <t>Dùng Iuno để vượt Tháp Nguy Hiểm từ Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Vực Nguy Hiểm</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Weapon Ultimate Form</t>
+          <t>Hình Thái Tối Thượng Của Vũ Khí</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Weapon Form Evolved</t>
+          <t>Vũ Khí Đã Tiến Hóa</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Resonator Skill Evolved</t>
+          <t>Kỹ năng Resonator Tiến hóa</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Chọn Vũ khí Mới</t>
+          <t>Chọn Vũ Khí Mới</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Chọn Vật phẩm Mới</t>
+          <t>Chọn Vật Phẩm Mới</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Nhận Phần thưởng Rương</t>
+          <t>Đã Nhận Phần Thưởng Rương</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Khe này không khả dụng trong giai đoạn này</t>
+          <t>Ô này không khả dụng trong giai đoạn này</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Làn sóng tiếp theo</t>
+          <t>Làn Sóng Tiếp Theo</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Synergistic Evo</t>
+          <t>Tiến Hóa Cộng Hưởng</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Resonators</t>
+          <t>Resonator</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Base Form</t>
+          <t>Hình Thái Cơ Bản</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Advanced Form</t>
+          <t>Hình Thái Cao Cấp</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Superior Form</t>
+          <t>Hình Thái Cao Cấp</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Ultimate Form I</t>
+          <t>Hình Thái Tối Thượng I</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Ultimate Form II</t>
+          <t>Hình Thái Tối Thượng II</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Chưa có Chiến Thuật</t>
+          <t>Chưa có Chiến thuật nào</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Insufficient Sim Creditss</t>
+          <t>Không đủ Tín Dụng Sim</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Vật Phẩm</t>
+          <t>Tác dụng vật phẩm</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Freezing Pulse</t>
+          <t>Xung Lạnh Đóng Băng</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Shock Pulse</t>
+          <t>Xung Kích Điện</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Matrix Command: Modulation</t>
+          <t>Lệnh Ma trận: Modulation</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Weapon Nâng cấp</t>
+          <t>Nâng Cấp Vũ Khí</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Amplifier Beacon</t>
+          <t>Đèn Tín Hiệu Khuếch Đại</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Magma Pulse</t>
+          <t>Xung Nhiệt Dung Nham</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Matrix Command: Overload</t>
+          <t>Lệnh Ma trận: Quá Tải</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Terminal Swap Success</t>
+          <t>Hoán Đổi Thiết Bị Đầu Cuối Thành Công</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Tiếp</t>
+          <t>Tiếp theo</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Đã đặt lại cài đặt</t>
+          <t>Đã khôi phục cài đặt về mặc định</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Catcher in the Tide</t>
+          <t>Người Bắt Giữ Trong Làn Sóng</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Đã hạ thấp độ khó</t>
+          <t>Độ khó đã được hạ xuống</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cindertide</t>
+          <t>Giấc Mơ Của Tro Tàn</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Dreams of Cindertide: Finale</t>
+          <t>Giấc Mơ Tro Tàn: Khúc Kết</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Turbulent Surge</t>
+          <t>Bão Tố Cuồn Cuộn</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Moments Scattered to the Wind</t>
+          <t>Khoảnh khắc bay theo gió</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Cấp Độ</t>
+          <t>Cấp độ</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Max HP</t>
+          <t>Tối đa HP</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Physical DMG Bonus</t>
+          <t>Tăng DMG Vật lý</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus</t>
+          <t>Thêm Sát Thương Băng giá</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus</t>
+          <t>Thêm Sát Thương Hợp Thể</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Electro DMG Bonus</t>
+          <t>Thêm Sát Thương Electro</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus</t>
+          <t>Tăng Sát Thương Aero</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Spectro DMG Bonus</t>
+          <t>Thêm Sát Thương Spectro</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus</t>
+          <t>Tăng Sát Thương Havoc</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>HP Regen</t>
+          <t>Hồi HP</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>DEF Penetration</t>
+          <t>XUYÊN PHÒNG NGỤ</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Tốc độ di chuyển</t>
+          <t>Tốc Độ Di Chuyển</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Tất cả DMG Bonus</t>
+          <t>Tăng Tất Cả Sát Thương</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>DMG Multiplier Bonus</t>
+          <t>Thêm Hệ Số Sát Thương</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Attack Speed Bonus</t>
+          <t>Thưởng Tốc Độ Tấn Công</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Pickup Range</t>
+          <t>Tầm Nhặt</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>New Mechanism</t>
+          <t>Cơ Chế Mới</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Thưởng Chỉ Số</t>
+          <t>Tăng thuộc tính</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>New Vật phẩm</t>
+          <t>Vật Phẩm Mới</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Mở khóa vật phẩm</t>
+          <t>Mở khóa Vật phẩm</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Mở khóa vật phẩm</t>
+          <t>Mở khóa Vật phẩm</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Mở khóa vật phẩm</t>
+          <t>Mở khóa Vật phẩm</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Mở khóa vật phẩm</t>
+          <t>Mở khóa Vật phẩm</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Mở khóa vật phẩm</t>
+          <t>Mở khóa Vật phẩm</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Mở khóa vật phẩm</t>
+          <t>Mở khóa Vật phẩm</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Mở khóa vật phẩm</t>
+          <t>Mở khóa Vật phẩm</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Mở khóa vật phẩm</t>
+          <t>Mở khóa Vật phẩm</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Compound Interest</t>
+          <t>Lãi Kép</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Part Exchange</t>
+          <t>Trao đổi bộ phận</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Family Takeover</t>
+          <t>Thâu Tóm Gia Tộc</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Asset Momentum</t>
+          <t>Đà Tài Nguyên</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Liquidation</t>
+          <t>Thanh Lý</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Montelli Financing</t>
+          <t>Tài Chính Montelli</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Options Trading</t>
+          <t>Giao Dịch Quyền Chọn</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Wealth Shock</t>
+          <t>Sốc Giàu Sang</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>High-Stakes Gambler</t>
+          <t>Con Bạc Mạo Hiểm</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Wall Fortification</t>
+          <t>Củng Cố Tường</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Tận Dụng Thế Mạnh</t>
+          <t>Tận dụng thế mạnh</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Aggressive Investment</t>
+          <t>Đầu Tư Mạnh Tay</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Cross-Border Trade</t>
+          <t>Giao Thương Biên Giới</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Philanthropist</t>
+          <t>Nhà Từ Thiện</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Crit Ban</t>
+          <t>Tỷ Lệ Bạo Kích</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Hedge Fund</t>
+          <t>Quỹ Đầu Tư Phòng Ngừa Rủi Ro</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Healing Ban</t>
+          <t>Cấm Hồi Phục</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Thật sự Estate</t>
+          <t>Bất động sản</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Chest Hunter</t>
+          <t>Thợ Săn Rương</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Lucky Blessing</t>
+          <t>Phước Lành May Mắn</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Golden Blessing</t>
+          <t>Phước Lành Hoàng Kim</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Crit Boost</t>
+          <t>Tăng Tỷ Lệ Bạo Kích</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Speed Boost</t>
+          <t>Tăng Tốc</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Survival Boost</t>
+          <t>Tăng cường sinh tồn</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Attack Boost</t>
+          <t>Tăng Tấn Công</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Discord Slayer</t>
+          <t>Kẻ Diệt Discord</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Treasure Raider</t>
+          <t>Kẻ Cướp Kho Báu</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Endurance</t>
+          <t>Sức Bền</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Hiệu Suất</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Thời Đại Hoàng Kim</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Far Sight</t>
+          <t>Tầm Nhìn Xa</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Ngày Trading</t>
+          <t>Giao Dịch Trong Ngày</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Leverage Effect</t>
+          <t>Hiệu ứng Đòn bẩy</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Elite Killer</t>
+          <t>Sát Thủ Cấp Tinh Anh</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Morph Boost</t>
+          <t>Tăng Cường Hóa Hình</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Close-Range Morph</t>
+          <t>Biến Hình Tầm Gần</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Morph Penetration</t>
+          <t>Xuyên Thấu Hóa Hình</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Bullet Boost</t>
+          <t>Tăng cường đạn</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Rapid Bullets</t>
+          <t>Đạn Liên Tục</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Long-Range Strike</t>
+          <t>Tấn Công Tầm Xa</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Beam Boost</t>
+          <t>Tăng Cường Tia Năng Lượng</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Over the Horizon</t>
+          <t>Vượt Qua Chân Trời</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Summon Boost</t>
+          <t>Triệu hồi Tăng Cường</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Resistance Break</t>
+          <t>Phá Vỡ Kháng Cự</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Summon Blessing</t>
+          <t>Triệu hồi Phúc Lành</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Spectro Boost</t>
+          <t>Tăng Cường Spectro</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Havoc Boost</t>
+          <t>Tăng Cường Havoc</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Aero Boost</t>
+          <t>Tăng cường Aero</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Fusion Boost</t>
+          <t>Tăng Cường Hợp Nhất</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Glacio Boost</t>
+          <t>Tăng Cường Glacio</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Electro Boost</t>
+          <t>Tăng Cường Electro</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Milestone Tasks</t>
+          <t>Nhiệm Vụ Cột Mốc</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Achievement Tasks</t>
+          <t>Nhiệm vụ Thành tựu</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai Đoạn Huấn Luyện 5</t>
+          <t>Hoàn thành Giai đoạn Huấn luyện 5</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai Đoạn Huấn Luyện 6</t>
+          <t>Hoàn thành Giai đoạn Huấn luyện 6</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai Đoạn Huấn Luyện 7</t>
+          <t>Hoàn thành Giai đoạn Huấn luyện 7</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Mở khóa 30 Mục trong Bộ sưu tập</t>
+          <t>Mở khóa 30 Vật Phẩm trong Phòng Trưng Bày</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Mở khóa 45 Mục trong Bộ sưu tập</t>
+          <t>Mở khóa 45 Vật Phẩm trong Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Mở khóa 55 Mục trong Bộ sưu tập</t>
+          <t>Mở khóa 55 Vật phẩm trong Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Mở khóa 2 Vũ khí trong Bộ sưu tập</t>
+          <t>Mở khóa 2 Vũ Khí trong Thư Viện</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Mở khóa 4 Vũ khí trong Bộ sưu tập</t>
+          <t>Mở khóa 4 Vũ Khí trong Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Mở khóa 8 Vũ khí trong Bộ sưu tập</t>
+          <t>Mở khóa 8 Vũ Khí trong Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Tiến hóa 1 vũ khí thành Dạng Tối thượng</t>
+          <t>Tiến hóa 1 vũ khí thành Hình Thái Tối Thượng</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Tiến hóa 2 vũ khí thành Dạng Tối thượng</t>
+          <t>Tiến hóa 2 vũ khí thành Hình Thái Tối Thượng</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Tiến hóa 4 vũ khí thành Dạng Tối thượng</t>
+          <t>Nâng cấp 4 vũ khí lên Hình Thái Tối Thượng</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Tiến hóa 6 vũ khí thành Dạng Tối thượng</t>
+          <t>Nâng cấp 6 vũ khí lên Hình Thái Tối Thượng</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Let The Bass Kick!</t>
+          <t>Để Bass lên ngôi!</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>ÔNG GIÀ</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Dizzy Girl</t>
+          <t>Cô Nàng Hoa Mắt</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Cấp Kỹ năng: ∞</t>
+          <t>Cấp Kỹ Năng: ∞</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Muse Dasher</t>
+          <t>Kẻ Nhảy Cảm Hứng</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Tôi sẽ cướp Pinball của bạn!</t>
+          <t>Ta sẽ cướp hết bóng pinball của ngươi!</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Yours Truly, A Pinball Master</t>
+          <t>Kính thư, Một Bậc Thầy Bi-a</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Chain Universe</t>
+          <t>Vũ Trụ Dây Xích</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Cosmic Trajectory Wanderer</t>
+          <t>Kẻ Lang Thang Quỹ Đạo Vũ Trụ</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Giữa Bạn và Vô cực</t>
+          <t>Giữa Anh và Vô Cực</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Giai đoạn 1</t>
+          <t>Giai Đoạn 1</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Giai đoạn 2</t>
+          <t>Giai Đoạn 2</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Giai đoạn 3</t>
+          <t>Giai Đoạn 3</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Giai đoạn 4</t>
+          <t>Giai Đoạn 4</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Giai đoạn 5</t>
+          <t>Giai Đoạn 5</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Giai đoạn 6</t>
+          <t>Giai Đoạn 6</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Giai đoạn 7</t>
+          <t>Giai Đoạn 7</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Nightmare</t>
+          <t>Ác Mộng</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Realistic</t>
+          <t>Chân thực</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Dễ thôi</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Chế độ Helltide</t>
+          <t>Chế Độ Hắc Triều</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Đang khoan</t>
+          <t>Đang Huấn Luyện</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Thời gian hoàn thành</t>
+          <t>Xóa bỏ Thời Gian</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Survival Time</t>
+          <t>Thời gian sinh tồn</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Insufficient Enhancement Modules</t>
+          <t>Mô-đun Tăng Cường không đủ</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Chế độ Helltide đã mở khóa</t>
+          <t>Chế Độ Hắc Triều đã mở khóa</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Cleared</t>
+          <t>Hoàn thành giải trừ</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Không thể sử dụng ô này trong giai đoạn này</t>
+          <t>Khe cắm không khả dụng ở giai đoạn này.</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Tổng Số Tiêu Diệt</t>
+          <t>Tổng Số Lần Tiêu Diệt</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Tactic Selection</t>
+          <t>Lựa Chọn Chiến Thuật</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Tactic Set Overview</t>
+          <t>Tổng Quan Bộ Chiến Thuật</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Không thể mang thêm</t>
+          <t>Không thể mang thêm được nữa</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Insufficient Sim Creditss</t>
+          <t>Không đủ Tín Dụng Sim</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Nút điều kiện trước chưa mở khóa</t>
+          <t>Điểm nút Điều kiện tiên quyết bị khóa</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Feilian Shock</t>
+          <t>Sốc Feilian</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Zenith Windblade</t>
+          <t>Kiếm Gió Zenith</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Sanguine Wheel</t>
+          <t>Bánh Xe Huyết</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Glittering Ray</t>
+          <t>Tia Sáng Lấp Lánh</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Rampant Fire</t>
+          <t>Lửa Hoang</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Explosive Omen</t>
+          <t>Điềm Báo Nổ</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Purchased</t>
+          <t>Đã mua</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Sử dụng Bộ trung hòa tần số để xóa</t>
+          <t>Dùng Frequency Neutralizer để dọn dẹp</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Vui lòng đợi nhiệm vụ mở khóa</t>
+          <t>Hãy chờ nhiệm vụ mở khóa</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Vui lòng đợi nhiệm vụ mở khóa</t>
+          <t>Hãy chờ nhiệm vụ mở khóa</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Vui lòng đợi nhiệm vụ mở khóa</t>
+          <t>Hãy chờ nhiệm vụ mở khóa</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Đang theo dõi</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Có Sẵn</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Ghi chép của thợ săn Cao nguyên Sanguis - Phần I</t>
+          <t>Ghi Chép Thợ Săn Cao Nguyên Sanguis - Phần I</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Ghi chép của thợ săn Cao nguyên Sanguis - Phần II</t>
+          <t>Ghi Chép Thợ Săn Cao Nguyên Sanguis - Phần II</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Wave Cleared</t>
+          <t>Đã vượt qua đợt tấn công</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Infinite Mode</t>
+          <t>Chế Độ Vô Tận</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Rời Đi Tạm Thời</t>
+          <t>Tạm rời đi đã</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Không thể lưu ở giai đoạn này, không thể tiếp tục</t>
+          <t>Giai đoạn này không thể lưu, không thể tiếp tục</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Mũi khoan mới đã mở khóa</t>
+          <t>Bài Tập Mới Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả thử thách Giấc mơ Tro tàn ở Cao nguyên Sanguis để mở khóa</t>
+          <t>Hoàn thành tất cả thử thách Giấc Mơ Tro Tàn ở Sanguis Plateaus để mở khóa</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Zephyr Symphony</t>
+          <t>Bản Giao Hưởng Zephyr</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Ashen Oath</t>
+          <t>Lời Thề Tro Tàn</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Waxing Moon</t>
+          <t>Trăng Lưỡi Liềm</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Breeze Breaker</t>
+          <t>Kẻ Phá Gió</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Cách mở khóa</t>
+          <t>Cách Mở Khóa</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Cách nhận</t>
+          <t>Cách chấp nhận</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Theo dõi</t>
+          <t>Bản nhạc</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Chọn Chiến thuật</t>
+          <t>Chọn Chiến Thuật</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Tactic Obtained</t>
+          <t>Đã Nhận Chiến Thuật</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Tactic Enhancement</t>
+          <t>Tăng Cường Chiến Thuật</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Không thể tiến hành ở Chế độ Co-op</t>
+          <t>Không thể tiếp tục ở Chế độ Hợp Tác</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Hành trình mới đang chờ đợi</t>
+          <t>Hành trình mới đang chờ đón</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Sigil</t>
+          <t>Ấn Tín</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Divined Dream</t>
+          <t>Giấc Mộng Tiên Tri</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Theo dõi</t>
+          <t>Bản nhạc</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Tiến hành để mở khóa</t>
+          <t>Tiến hành mở khóa</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Đã chọn Chiến thuật</t>
+          <t>Chiến Thuật Đã Chọn</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Giai đoạn bị khóa</t>
+          <t>Sân khấu bị khóa.</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Chế độ Helltide</t>
+          <t>Chế Độ Hắc Triều</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Available Quests</t>
+          <t>Nhiệm vụ khả dụng</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Hãy tiếp tục thực hiện nhiệm vụ để mở khóa</t>
+          <t>Hãy hoàn thành các nhiệm vụ để mở khóa</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Hãy tiếp tục thực hiện nhiệm vụ để mở khóa</t>
+          <t>Hãy hoàn thành các nhiệm vụ để mở khóa</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Hãy tiếp tục khám phá khu vực</t>
+          <t>Hãy tiếp tục khám phá khu vực này</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Mingting</t>
+          <t>Minh Đình</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Bambooscape</t>
+          <t>Cảnh Tre</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Gan Ziqi</t>
+          <t>Cảm Tử Kỳ</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
